--- a/education_surveys/006_survey_on_early_music_instruction--education_surveys.xlsx
+++ b/education_surveys/006_survey_on_early_music_instruction--education_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C59"/>
+  <dimension ref="A1:C55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1840,7 +1840,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>perceived_benefits_of_early_music_instruction_2_choices</t>
+          <t>perceived_benefits_of_early_instrument_education_3_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1862,36 +1862,36 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>fine_motor_skills</t>
+          <t>language_development</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Fine Motor Skills</t>
+          <t>Language Development</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>perceived_benefits_of_early_instrument_education_3_choices</t>
+          <t>perceived_benefits_of_early_vocal_education_3_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>language_development</t>
+          <t>emotional_regulation</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Language Development</t>
+          <t>Emotional Regulation</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>perceived_benefits_of_early_instrument_education_3_choices</t>
+          <t>perceived_benefits_of_early_vocal_education_3_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1908,24 +1908,24 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>perceived_benefits_of_early_vocal_education_3_choices</t>
+          <t>perceived_benefits_of_early_music_instruction_3_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>emotional_regulation</t>
+          <t>emotional_intelligence</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Emotional Regulation</t>
+          <t>Emotional Intelligence</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>perceived_benefits_of_early_vocal_education_3_choices</t>
+          <t>perceived_benefits_of_early_music_instruction_3_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1942,7 +1942,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>perceived_benefits_of_early_vocal_education_3_choices</t>
+          <t>perceived_benefits_of_early_music_instruction_3_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1959,58 +1959,58 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>perceived_benefits_of_early_music_instruction_3_choices</t>
+          <t>perceived_benefits_of_early_instrument_education_4_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>emotional_intelligence</t>
+          <t>fine_motor_skills</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Emotional Intelligence</t>
+          <t>Fine Motor Skills</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>perceived_benefits_of_early_music_instruction_3_choices</t>
+          <t>perceived_benefits_of_early_instrument_education_4_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>fine_motor_skills</t>
+          <t>emotional_regulation</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Fine Motor Skills</t>
+          <t>Emotional Regulation</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>perceived_benefits_of_early_music_instruction_3_choices</t>
+          <t>perceived_benefits_of_early_vocal_education_4_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>emotional_regulation</t>
+          <t>social_skills</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Emotional Regulation</t>
+          <t>Social Skills</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>perceived_benefits_of_early_instrument_education_4_choices</t>
+          <t>perceived_benefits_of_early_vocal_education_4_choices</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2027,83 +2027,15 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>perceived_benefits_of_early_instrument_education_4_choices</t>
+          <t>perceived_benefits_of_early_vocal_education_4_choices</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>emotional_regulation</t>
+          <t>language_development</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
-        <is>
-          <t>Emotional Regulation</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>perceived_benefits_of_early_instrument_education_4_choices</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>fine_motor_skills</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Fine Motor Skills</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>perceived_benefits_of_early_vocal_education_4_choices</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>social_skills</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Social Skills</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>perceived_benefits_of_early_vocal_education_4_choices</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>fine_motor_skills</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Fine Motor Skills</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>perceived_benefits_of_early_vocal_education_4_choices</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>language_development</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
         <is>
           <t>Language Development</t>
         </is>
